--- a/storage/app/assessTemplate/piloti.xlsx
+++ b/storage/app/assessTemplate/piloti.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739D0D32-4816-4ED1-967D-D5C5A468A01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AF7E85-C01F-4B4B-95CD-7DF85FA15621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{0297FCB9-249A-495F-A212-31CBE356A93C}"/>
+    <workbookView xWindow="45" yWindow="765" windowWidth="28755" windowHeight="15435" xr2:uid="{0297FCB9-249A-495F-A212-31CBE356A93C}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（ピロティー付）" sheetId="3" r:id="rId1"/>
@@ -333,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="#,##0.0;[Red]\-#,##0.0"/>
     <numFmt numFmtId="177" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="178" formatCode="#,##0&quot;千円&quot;"/>
@@ -342,6 +342,7 @@
     <numFmt numFmtId="181" formatCode="0.0%"/>
     <numFmt numFmtId="182" formatCode="#,##0&quot;年&quot;"/>
     <numFmt numFmtId="183" formatCode="0;_ꐀ"/>
+    <numFmt numFmtId="184" formatCode="ggge&quot;年&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1225,88 +1226,6 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="40" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1355,11 +1274,93 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1704,8 +1705,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
       <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,47 +1716,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="106"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="83"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="106"/>
-      <c r="N4" s="110"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -1763,8 +1764,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1793,12 +1794,12 @@
     </row>
     <row r="7" spans="1:15" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="97"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="99"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="87"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="89"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="73"/>
       <c r="J7" s="15" t="s">
         <v>9</v>
       </c>
@@ -1866,13 +1867,13 @@
       <c r="D12" s="21"/>
       <c r="E12" s="1"/>
       <c r="F12" s="17"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="99"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="73"/>
       <c r="J12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="100"/>
-      <c r="L12" s="101"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="75"/>
       <c r="M12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1903,27 +1904,27 @@
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="11"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="81"/>
-      <c r="E15" s="83" t="s">
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
+      <c r="E15" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="75"/>
+      <c r="H15" s="95"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="74" t="s">
+      <c r="J15" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="75"/>
+      <c r="K15" s="95"/>
       <c r="N15" s="13"/>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="11"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="E16" s="84"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="E16" s="93"/>
       <c r="G16" s="25" t="s">
         <v>17</v>
       </c>
@@ -1945,11 +1946,11 @@
         <v>20</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="91"/>
-      <c r="F17" s="76" t="s">
+      <c r="E17" s="103"/>
+      <c r="F17" s="102" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="30"/>
@@ -1965,9 +1966,9 @@
         <v>23</v>
       </c>
       <c r="C18" s="28"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="76"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="102"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
       <c r="I18" s="32"/>
@@ -1981,9 +1982,9 @@
         <v>24</v>
       </c>
       <c r="C19" s="28"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="76"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="102"/>
       <c r="G19" s="36"/>
       <c r="H19" s="37"/>
       <c r="I19" s="32"/>
@@ -2004,27 +2005,27 @@
     </row>
     <row r="22" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="11"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="E22" s="83" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="E22" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="74" t="s">
+      <c r="G22" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="75"/>
+      <c r="H22" s="95"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="74" t="s">
+      <c r="J22" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="75"/>
+      <c r="K22" s="95"/>
       <c r="N22" s="13"/>
     </row>
     <row r="23" spans="1:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="11"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="E23" s="84"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="E23" s="93"/>
       <c r="G23" s="25" t="s">
         <v>17</v>
       </c>
@@ -2070,27 +2071,27 @@
     </row>
     <row r="27" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="E27" s="87" t="s">
+      <c r="B27" s="96"/>
+      <c r="C27" s="96"/>
+      <c r="E27" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="89" t="s">
+      <c r="G27" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="90"/>
+      <c r="H27" s="101"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="89" t="s">
+      <c r="J27" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="K27" s="90"/>
+      <c r="K27" s="101"/>
       <c r="N27" s="13"/>
     </row>
     <row r="28" spans="1:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="11"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="E28" s="88"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="E28" s="99"/>
       <c r="G28" s="39" t="s">
         <v>17</v>
       </c>
@@ -2112,11 +2113,11 @@
         <v>20</v>
       </c>
       <c r="C29" s="28"/>
-      <c r="D29" s="76" t="s">
+      <c r="D29" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="79"/>
-      <c r="F29" s="76" t="s">
+      <c r="E29" s="105"/>
+      <c r="F29" s="102" t="s">
         <v>22</v>
       </c>
       <c r="G29" s="30"/>
@@ -2132,9 +2133,9 @@
         <v>23</v>
       </c>
       <c r="C30" s="28"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="76"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="102"/>
       <c r="G30" s="34"/>
       <c r="H30" s="35"/>
       <c r="I30" s="32"/>
@@ -2148,9 +2149,9 @@
         <v>24</v>
       </c>
       <c r="C31" s="28"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="76"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="102"/>
       <c r="G31" s="36"/>
       <c r="H31" s="37"/>
       <c r="I31" s="32"/>
@@ -2164,28 +2165,28 @@
     </row>
     <row r="33" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="11"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81" t="s">
+      <c r="B33" s="90"/>
+      <c r="C33" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="83" t="s">
+      <c r="E33" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="72" t="s">
+      <c r="G33" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="73"/>
-      <c r="J33" s="74" t="s">
+      <c r="H33" s="108"/>
+      <c r="J33" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="75"/>
+      <c r="K33" s="95"/>
       <c r="N33" s="13"/>
     </row>
     <row r="34" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="11"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="E34" s="84"/>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
+      <c r="E34" s="93"/>
       <c r="G34" s="41"/>
       <c r="H34" s="26" t="s">
         <v>30</v>
@@ -2202,11 +2203,11 @@
         <v>20</v>
       </c>
       <c r="C35" s="42"/>
-      <c r="D35" s="76" t="s">
+      <c r="D35" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="77"/>
-      <c r="F35" s="76" t="s">
+      <c r="E35" s="109"/>
+      <c r="F35" s="102" t="s">
         <v>22</v>
       </c>
       <c r="G35" s="43"/>
@@ -2222,9 +2223,9 @@
         <v>23</v>
       </c>
       <c r="C36" s="42"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="76"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="46"/>
       <c r="H36" s="47"/>
       <c r="I36" s="45"/>
@@ -2238,9 +2239,9 @@
         <v>24</v>
       </c>
       <c r="C37" s="42"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="76"/>
+      <c r="D37" s="102"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="102"/>
       <c r="G37" s="48"/>
       <c r="H37" s="49"/>
       <c r="I37" s="45"/>
@@ -2342,6 +2343,35 @@
     <row r="81" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="H12:I12"/>
@@ -2355,35 +2385,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
